--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38870-2026 artfynd.xlsx
+++ b/artfynd/A 38870-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858392</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858391</v>
       </c>
       <c r="B3" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858393</v>
       </c>
       <c r="B4" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
